--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_366_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_366_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1378</v>
+        <v>4.5424</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1322</v>
+        <v>3.604</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0056</v>
+        <v>0.9384</v>
       </c>
       <c r="G2" t="n">
         <v>3.4281</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0789</v>
+        <v>-0.6743</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1827</v>
+        <v>-0.25</v>
       </c>
       <c r="V2" t="n">
         <v>1.3247</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2538</v>
+        <v>3.9272</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7616</v>
+        <v>4.2334</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5078</v>
+        <v>-0.3062</v>
       </c>
       <c r="G3" t="n">
         <v>0.07539999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9506</v>
+        <v>-0.2772</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0455</v>
+        <v>-0.5737</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0949</v>
+        <v>0.2965</v>
       </c>
       <c r="V3" t="n">
         <v>4.8249</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0298</v>
+        <v>2.2892</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4672</v>
+        <v>2.9954</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4374</v>
+        <v>-0.7062</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0946</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6606</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6018</v>
+        <v>0.13</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0587</v>
+        <v>0.7899</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.625</v>
+        <v>2.2547</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3699</v>
+        <v>2.134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2552</v>
+        <v>0.1207</v>
       </c>
       <c r="G5" t="n">
         <v>0.1198</v>
@@ -844,13 +844,13 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0439</v>
+        <v>-0.3264</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0703</v>
+        <v>-0.2047</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8287</v>
+        <v>-0.2068</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.039</v>
+        <v>-0.3748</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7897</v>
+        <v>0.1681</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1124</v>
+        <v>-1.6859</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8104</v>
+        <v>0.7565</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.302</v>
+        <v>-2.4424</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9935</v>
+        <v>0.8475</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7458</v>
+        <v>0.2353</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2477</v>
+        <v>0.6122</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.119</v>
+        <v>-2.5334</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.5213</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0543</v>
+        <v>-3.0547</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5157</v>
+        <v>-0.8404</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4015</v>
+        <v>0.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8631</v>
+        <v>-0.4547</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7287</v>
+        <v>1.1743</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1344</v>
+        <v>-1.629</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6859</v>
+        <v>-1.2439</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7565</v>
+        <v>0.4357</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4424</v>
+        <v>-1.6796</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8475</v>
+        <v>0.0032</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2353</v>
+        <v>-0.1072</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6122</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5334</v>
+        <v>-1.2472</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5213</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.0547</v>
+        <v>-1.79</v>
       </c>
       <c r="P7" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.3195</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.5515</v>
-      </c>
       <c r="S7" t="n">
-        <v>-1.4967</v>
+        <v>-0.3705</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3443</v>
+        <v>-0.3497</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1524</v>
+        <v>-0.0209</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1618</v>
+        <v>-1.3169</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7025</v>
+        <v>-0.3929</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8643</v>
+        <v>-0.9241</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2439</v>
+        <v>-3.1124</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4357</v>
+        <v>-0.8104</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6796</v>
+        <v>-2.302</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0032</v>
+        <v>-0.9935</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1072</v>
+        <v>-0.7458</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>-0.2477</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2472</v>
+        <v>-2.119</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5427999999999999</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.79</v>
+        <v>-2.0543</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0776</v>
+        <v>0.0275</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.2396</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2561</v>
+        <v>0.2671</v>
       </c>
       <c r="V8" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.6805</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.6805</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8914</v>
+        <v>-3.7335</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7088</v>
+        <v>-2.4165</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1826</v>
+        <v>-1.317</v>
       </c>
       <c r="G9" t="n">
         <v>0.3914</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1448</v>
+        <v>0.3027</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5272</v>
+        <v>-0.1806</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6177</v>
+        <v>0.4832</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2525</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>7.3014</v>
+        <v>7.301600000000001</v>
       </c>
       <c r="E10" t="n">
         <v>10.9569</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6554</v>
+        <v>-3.6553</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1221</v>
@@ -1234,13 +1234,13 @@
         <v>16.2366</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2388</v>
+        <v>-1.2387</v>
       </c>
       <c r="T10" t="n">
         <v>-2.7501</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5113</v>
+        <v>1.5111</v>
       </c>
       <c r="V10" t="n">
         <v>8.183299999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.3079</v>
+        <v>4.2673</v>
       </c>
       <c r="E11" t="n">
-        <v>7.2273</v>
+        <v>7.8171</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9194</v>
+        <v>-3.5498</v>
       </c>
       <c r="G11" t="n">
         <v>6.8008</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4361</v>
+        <v>-0.4766</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1123</v>
+        <v>-0.5226</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3238</v>
+        <v>0.0459</v>
       </c>
       <c r="V11" t="n">
         <v>-3.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7668</v>
+        <v>2.2551</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2361</v>
+        <v>3.59</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4693</v>
+        <v>-1.3349</v>
       </c>
       <c r="G12" t="n">
         <v>2.4527</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3664</v>
+        <v>0.1219</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2003</v>
+        <v>0.1535</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1661</v>
+        <v>-0.0316</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2888</v>
+        <v>1.02</v>
       </c>
       <c r="E13" t="n">
         <v>1.3694</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0806</v>
+        <v>-0.3494</v>
       </c>
       <c r="G13" t="n">
         <v>1.2213</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8988</v>
+        <v>-1.1677</v>
       </c>
       <c r="T13" t="n">
         <v>-0.8962</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0026</v>
+        <v>-0.2715</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4254</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5271</v>
+        <v>0.4599</v>
       </c>
       <c r="E15" t="n">
         <v>0.335</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1921</v>
+        <v>0.1249</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2812</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5764</v>
+        <v>0.5091</v>
       </c>
       <c r="T15" t="n">
         <v>0.2478</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3286</v>
+        <v>0.2614</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0375</v>
+        <v>-0.6944</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5692</v>
+        <v>0.9794</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6067</v>
+        <v>-1.6739</v>
       </c>
       <c r="G16" t="n">
         <v>1.2052</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>2.381</v>
+        <v>1.724</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3056</v>
+        <v>0.7158</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0754</v>
+        <v>1.0082</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9063</v>
+        <v>-1.6526</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4776</v>
+        <v>-1.8878</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5713</v>
+        <v>0.2352</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8826000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2082</v>
+        <v>0.4619</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.963</v>
+        <v>-0.3732</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1712</v>
+        <v>0.8351</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5361</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3369</v>
+        <v>-2.2024</v>
       </c>
       <c r="E18" t="n">
         <v>-2.5514</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2145</v>
+        <v>0.349</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1253</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1801</v>
+        <v>0.3145</v>
       </c>
       <c r="T18" t="n">
         <v>0.0905</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4287</v>
+        <v>-4.1707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4462</v>
+        <v>-1.3898</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9825</v>
+        <v>-2.7809</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7214</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6536999999999999</v>
+        <v>-0.0883</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4604</v>
+        <v>-0.4832</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1933</v>
+        <v>0.3949</v>
       </c>
       <c r="V19" t="n">
         <v>-3.7527</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.1981</v>
+        <v>-7.2989</v>
       </c>
       <c r="E20" t="n">
         <v>-6.6189</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5793</v>
+        <v>-0.6801</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6439</v>
@@ -2014,13 +2014,13 @@
         <v>2.5515</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0901</v>
+        <v>-0.0108</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3927</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4828</v>
+        <v>0.382</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3247</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.3016</v>
+        <v>-7.3014</v>
       </c>
       <c r="E21" t="n">
-        <v>3.6553</v>
+        <v>3.655400000000002</v>
       </c>
       <c r="F21" t="n">
         <v>-10.957</v>
@@ -2092,10 +2092,10 @@
         <v>12.7575</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2388</v>
+        <v>1.2386</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5112</v>
+        <v>-1.5113</v>
       </c>
       <c r="U21" t="n">
         <v>2.75</v>
